--- a/data/contractors/c1.xlsx
+++ b/data/contractors/c1.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R9a1c76b44ca847a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" r:id="R8b5cd00cc5a345db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Модель" sheetId="3" r:id="R602559009eea40ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DATA" sheetId="4" r:id="Rd1b4e91ba7a1424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R2a2e2ec1c32042c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" r:id="R5359cb7b9ad14ec0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Модель" sheetId="3" r:id="Ra5288770da324bf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DATA" sheetId="4" r:id="R3e31d386b0b043d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5446,7 +5446,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>{"application":"financial-economic-model","fileType":"contractor","schemaVersion":1,"savedAt":"2026-09-22T19:09:48.659Z","contractor":{"id":"c1","name":"Подрядчик 1","contracts":[{"id":"d1","number":"ПС-250/24","name":"Строительно-монтажные работы","currency":"RUB","fx":1,"vatRate":22,"parameters":{"payroll":{"value":150000,"enabled":true,"method":"monthly"},"payrollTax":{"value":13,"enabled":true,"method":"rate"},"insurance":{"value":30.9,"enabled":true,"method":"rate"},"vacation":{"value":8,"enabled":true,"method":"rate"},"subcontract":{"value":0,"enabled":true,"method":"percentRevenue"},"equipment":{"value":5000,"enabled":true,"method":"unit"},"scaffolding":{"value":0,"enabled":true,"method":"manual"},"scaffoldLabor":{"value":1500,"enabled":true,"method":"unit"},"projectMaterials":{"value":100,"enabled":true,"method":"materials"},"consumables":{"value":10,"enabled":true,"method":"percentPayroll"},"nrk":{"value":4000,"enabled":true,"method":"unit"},"otherDirect":{"value":0,"enabled":true,"method":"manual"},"indirectPayroll":{"value":180000,"enabled":true,"method":"monthly"},"indirectTax":{"value":13,"enabled":true,"method":"rate"},"indirectInsurance":{"value":30.9,"enabled":true,"method":"rate"},"indirectVacation":{"value":8,"enabled":true,"method":"rate"},"food":{"value":650,"enabled":true,"method":"day"},"housing":{"value":500,"enabled":true,"method":"day"},"bus":{"value":639344,"enabled":true,"method":"unit"},"car":{"value":319672,"enabled":true,"method":"unit"},"formwork":{"value":0,"enabled":true,"method":"manual"},"ppe":{"value":30000,"enabled":true,"method":"annualPerPerson"},"tickets":{"value":40000,"enabled":true,"method":"rotation"},"permit":{"value":8000,"enabled":true,"method":"perPerson"},"medical":{"value":3000,"enabled":true,"method":"perPerson"},"vziz":{"value":20000,"enabled":true,"method":"annualPerPerson"},"office":{"value":300000,"enabled":true,"method":"monthly"},"warehouse":{"value":800000,"enabled":true,"method":"monthly"},"internet":{"value":0,"enabled":true,"method":"monthly"},"waste":{"value":0,"enabled":true,"method":"monthly"},"safety":{"value":1,"enabled":true,"method":"percentPayroll"},"accident":{"value":5000,"enabled":true,"method":"annualPerPerson"},"it":{"value":0,"enabled":true,"method":"manual"},"containers":{"value":0,"enabled":true,"method":"manual"},"modularOffice":{"value":0,"enabled":true,"method":"manual"},"transport":{"value":0,"enabled":true,"method":"manual"},"otherIndirect":{"value":10,"enabled":true,"method":"percentDirect"}},"sources":{},"versions":[{"id":"v1","name":"Базовая 01.08.2026","created":"2026-09-22","drivers":{"revenue":[0,25000000,48000000,64000000,82000000,108000000,125000000,142000000,155000000,168000000,150000000,115000000],"materials":[0,4000000,7000000,10000000,12000000,17000000,20000000,23000000,26000000,28000000,25000000,18000000],"directPeople":[0,25,45,62,78,94,108,118,125,128,115,90],"indirectPeople":[8,12,18,25,30,34,38,40,42,42,36,28],"equipmentHours":[0,400,750,1100,1450,1800,2100,2300,2450,2400,1900,1200],"nrkVolume":[0,0,0,10,25,40,55,70,82,90,60,30],"payments":[0,0,20000000,35000000,55000000,72000000,95000000,115000000,128000000,145000000,150000000,130000000],"advances":[25000000,0,0,0,0,0,0,0,0,0,0,0],"advanceOffset":[0,0,5000000,5000000,5000000,5000000,5000000,0,0,0,0,0],"factoring":[0,0,0,0,0,0,0,0,0,0,0,0],"guaranteeRate":5,"otherRevenue":[0,0,0,0,0,0,0,0,0,0,0,0]},"parameters":{"payroll":{"value":150000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"payrollTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"insurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"vacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"subcontract":{"value":0,"method":"percentRevenue","enabled":true,"lag":0,"cash":true,"vat":true},"equipment":{"value":5000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"scaffolding":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"scaffoldLabor":{"value":1500,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"projectMaterials":{"value":100,"method":"materials","enabled":true,"lag":0,"cash":true,"vat":true},"consumables":{"value":10,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"nrk":{"value":4000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"otherDirect":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"indirectPayroll":{"value":180000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"indirectTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectInsurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectVacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"food":{"value":650,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"housing":{"value":500,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"bus":{"value":639344,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"car":{"value":319672,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"formwork":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"ppe":{"value":30000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"tickets":{"value":40000,"method":"rotation","enabled":true,"lag":0,"cash":true,"vat":true},"permit":{"value":8000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"medical":{"value":3000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"vziz":{"value":20000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"office":{"value":300000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"warehouse":{"value":800000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"internet":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"waste":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"safety":{"value":1,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"accident":{"value":5000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"it":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"containers":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"modularOffice":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"transport":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"otherIndirect":{"value":10,"method":"percentDirect","enabled":true,"lag":0,"cash":true,"vat":true}},"year":2026,"vatRate":22,"vacationBasis":"annual","bindings":{},"manualCosts":{},"manualPayments":{},"dataMode":"demo"},{"id":"v2","name":"Текущая 22.09.2026","created":"2026-09-22","drivers":{"revenue":[0,25000000,48000000,64000000,82000000,108000000,132500000,150520000,164300000,178080000,159000000,121900000],"materials":[0,4000000,7000000,10000000,12000000,17000000,20000000,23000000,26000000,28000000,25000000,18000000],"directPeople":[0,25,45,62,78,94,108,118,125,128,115,90],"indirectPeople":[8,12,18,25,30,34,38,40,42,42,36,28],"equipmentHours":[0,400,750,1100,1450,1800,2100,2300,2450,2400,1900,1200],"nrkVolume":[0,0,0,10,25,40,55,70,82,90,60,30],"payments":[0,0,20000000,35000000,55000000,72000000,95000000,115000000,128000000,145000000,150000000,130000000],"advances":[25000000,0,0,0,0,0,0,0,0,0,0,0],"advanceOffset":[0,0,5000000,5000000,5000000,5000000,5000000,0,0,0,0,0],"factoring":[0,0,0,0,0,0,0,0,0,0,0,0],"guaranteeRate":5,"otherRevenue":[0,0,0,0,0,0,0,0,0,0,0,0]},"parameters":{"payroll":{"value":150000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"payrollTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"insurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"vacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"subcontract":{"value":0,"method":"percentRevenue","enabled":true,"lag":0,"cash":true,"vat":true},"equipment":{"value":5000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"scaffolding":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"scaffoldLabor":{"value":1500,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"projectMaterials":{"value":100,"method":"materials","enabled":true,"lag":0,"cash":true,"vat":true},"consumables":{"value":10,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"nrk":{"value":4000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"otherDirect":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"indirectPayroll":{"value":180000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"indirectTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectInsurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectVacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"food":{"value":650,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"housing":{"value":500,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"bus":{"value":639344,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"car":{"value":319672,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"formwork":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"ppe":{"value":30000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"tickets":{"value":40000,"method":"rotation","enabled":true,"lag":0,"cash":true,"vat":true},"permit":{"value":8000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"medical":{"value":3000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"vziz":{"value":20000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"office":{"value":300000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"warehouse":{"value":800000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"internet":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"waste":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"safety":{"value":1,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"accident":{"value":5000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"it":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"containers":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"modularOffice":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"transport":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"otherIndirect":{"value":10,"method":"percentDirect","enabled":true,"lag":0,"cash":true,"vat":true}},"year":2026,"vatRate":22,"vacationBasis":"annual","bindings":{},"manualCosts":{},"manualPayments":{},"dataMode":"demo"}],"sourceProfiles":{},"year":2026,"vacationBasis":"annual"},{"id":"d2","number":"ПС-251/24","name":"Дополнительные работы","currency":"RUB","fx":1,"vatRate":22,"parameters":{"payroll":{"value":150000,"enabled":true,"method":"monthly"},"payrollTax":{"value":13,"enabled":true,"method":"rate"},"insurance":{"value":30.9,"enabled":true,"method":"rate"},"vacation":{"value":8,"enabled":true,"method":"rate"},"subcontract":{"value":0,"enabled":true,"method":"percentRevenue"},"equipment":{"value":5000,"enabled":true,"method":"unit"},"scaffolding":{"value":0,"enabled":true,"method":"manual"},"scaffoldLabor":{"value":1500,"enabled":true,"method":"unit"},"projectMaterials":{"value":100,"enabled":true,"method":"materials"},"consumables":{"value":10,"enabled":true,"method":"percentPayroll"},"nrk":{"value":4000,"enabled":true,"method":"unit"},"otherDirect":{"value":0,"enabled":true,"method":"manual"},"indirectPayroll":{"value":180000,"enabled":true,"method":"monthly"},"indirectTax":{"value":13,"enabled":true,"method":"rate"},"indirectInsurance":{"value":30.9,"enabled":true,"method":"rate"},"indirectVacation":{"value":8,"enabled":true,"method":"rate"},"food":{"value":650,"enabled":true,"method":"day"},"housing":{"value":500,"enabled":true,"method":"day"},"bus":{"value":639344,"enabled":true,"method":"unit"},"car":{"value":319672,"enabled":true,"method":"unit"},"formwork":{"value":0,"enabled":true,"method":"manual"},"ppe":{"value":30000,"enabled":true,"method":"annualPerPerson"},"tickets":{"value":40000,"enabled":true,"method":"rotation"},"permit":{"value":8000,"enabled":true,"method":"perPerson"},"medical":{"value":3000,"enabled":true,"method":"perPerson"},"vziz":{"value":20000,"enabled":true,"method":"annualPerPerson"},"office":{"value":300000,"enabled":true,"method":"monthly"},"warehouse":{"value":800000,"enabled":true,"method":"monthly"},"internet":{"value":0,"enabled":true,"method":"monthly"},"waste":{"value":0,"enabled":true,"method":"monthly"},"safety":{"value":1,"enabled":true,"method":"percentPayroll"},"accident":{"value":5000,"enabled":true,"method":"annualPerPerson"},"it":{"value":0,"enabled":true,"method":"manual"},"containers":{"value":0,"enabled":true,"method":"manual"},"modularOffice":{"value":0,"enabled":true,"method":"manual"},"transport":{"value":0,"enabled":true,"method":"manual"},"otherIndirect":{"value":10,"enabled":true,"method":"percentDirect"}},"sources":{},"versions":[{"id":"v_mucuctuh3k83","name":"Базовая","created":"2026-09-22","drivers":{"revenue":[0,25000000,48000000,64000000,82000000,108000000,125000000,142000000,155000000,168000000,150000000,115000000],"materials":[0,4000000,7000000,10000000,12000000,17000000,20000000,23000000,26000000,28000000,25000000,18000000],"directPeople":[0,25,45,62,78,94,108,118,125,128,115,90],"indirectPeople":[8,12,18,25,30,34,38,40,42,42,36,28],"equipmentHours":[0,400,750,1100,1450,1800,2100,2300,2450,2400,1900,1200],"nrkVolume":[0,0,0,10,25,40,55,70,82,90,60,30],"payments":[0,0,20000000,35000000,55000000,72000000,95000000,115000000,128000000,145000000,150000000,130000000],"advances":[25000000,0,0,0,0,0,0,0,0,0,0,0],"advanceOffset":[0,0,5000000,5000000,5000000,5000000,5000000,0,0,0,0,0],"factoring":[0,0,0,0,0,0,0,0,0,0,0,0],"guaranteeRate":5,"otherRevenue":[0,0,0,0,0,0,0,0,0,0,0,0]},"parameters":{"payroll":{"value":150000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"payrollTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"insurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"vacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"subcontract":{"value":0,"method":"percentRevenue","enabled":true,"lag":0,"cash":true,"vat":true},"equipment":{"value":5000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"scaffolding":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"scaffoldLabor":{"value":1500,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"projectMaterials":{"value":100,"method":"materials","enabled":true,"lag":0,"cash":true,"vat":true},"consumables":{"value":10,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"nrk":{"value":4000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"otherDirect":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"indirectPayroll":{"value":180000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"indirectTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectInsurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectVacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"food":{"value":650,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"housing":{"value":500,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"bus":{"value":639344,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"car":{"value":319672,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"formwork":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"ppe":{"value":30000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"tickets":{"value":40000,"method":"rotation","enabled":true,"lag":0,"cash":true,"vat":true},"permit":{"value":8000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"medical":{"value":3000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"vziz":{"value":20000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"office":{"value":300000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"warehouse":{"value":800000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"internet":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"waste":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"safety":{"value":1,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"accident":{"value":5000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"it":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"containers":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"modularOffice":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"transport":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"otherIndirect":{"value":10,"method":"percentDirect","enabled":true,"lag":0,"cash":true,"vat":true}},"year":2026,"vatRate":22,"vacationBasis":"annual","bindings":{},"manualCosts":{},"manualPayments":{},"dataMode":"demo"}],"sourceProfiles":{},"year":2026,"vacationBasis":"annual"}]}}</x:v>
+        <x:v>{"application":"financial-economic-model","fileType":"contractor","schemaVersion":1,"savedAt":"2026-09-22T19:54:08.829Z","contractor":{"id":"c1","name":"Подрядчик 1","contracts":[{"id":"d1","number":"ПС-250/24","name":"Строительно-монтажные работы","currency":"RUB","fx":1,"vatRate":22,"parameters":{"payroll":{"value":150000,"enabled":true,"method":"monthly"},"payrollTax":{"value":13,"enabled":true,"method":"rate"},"insurance":{"value":30.9,"enabled":true,"method":"rate"},"vacation":{"value":8,"enabled":true,"method":"rate"},"subcontract":{"value":0,"enabled":true,"method":"percentRevenue"},"equipment":{"value":5000,"enabled":true,"method":"unit"},"scaffolding":{"value":0,"enabled":true,"method":"manual"},"scaffoldLabor":{"value":1500,"enabled":true,"method":"unit"},"projectMaterials":{"value":100,"enabled":true,"method":"materials"},"consumables":{"value":10,"enabled":true,"method":"percentPayroll"},"nrk":{"value":4000,"enabled":true,"method":"unit"},"otherDirect":{"value":0,"enabled":true,"method":"manual"},"indirectPayroll":{"value":180000,"enabled":true,"method":"monthly"},"indirectTax":{"value":13,"enabled":true,"method":"rate"},"indirectInsurance":{"value":30.9,"enabled":true,"method":"rate"},"indirectVacation":{"value":8,"enabled":true,"method":"rate"},"food":{"value":650,"enabled":true,"method":"day"},"housing":{"value":500,"enabled":true,"method":"day"},"bus":{"value":639344,"enabled":true,"method":"unit"},"car":{"value":319672,"enabled":true,"method":"unit"},"formwork":{"value":0,"enabled":true,"method":"manual"},"ppe":{"value":30000,"enabled":true,"method":"annualPerPerson"},"tickets":{"value":40000,"enabled":true,"method":"rotation"},"permit":{"value":8000,"enabled":true,"method":"perPerson"},"medical":{"value":3000,"enabled":true,"method":"perPerson"},"vziz":{"value":20000,"enabled":true,"method":"annualPerPerson"},"office":{"value":300000,"enabled":true,"method":"monthly"},"warehouse":{"value":800000,"enabled":true,"method":"monthly"},"internet":{"value":0,"enabled":true,"method":"monthly"},"waste":{"value":0,"enabled":true,"method":"monthly"},"safety":{"value":1,"enabled":true,"method":"percentPayroll"},"accident":{"value":5000,"enabled":true,"method":"annualPerPerson"},"it":{"value":0,"enabled":true,"method":"manual"},"containers":{"value":0,"enabled":true,"method":"manual"},"modularOffice":{"value":0,"enabled":true,"method":"manual"},"transport":{"value":0,"enabled":true,"method":"manual"},"otherIndirect":{"value":10,"enabled":true,"method":"percentDirect"}},"sources":{},"versions":[{"id":"v1","name":"Базовая 01.08.2026","created":"2026-09-22","drivers":{"revenue":[0,25000000,48000000,64000000,82000000,108000000,125000000,142000000,155000000,168000000,150000000,115000000],"materials":[0,4000000,7000000,10000000,12000000,17000000,20000000,23000000,26000000,28000000,25000000,18000000],"directPeople":[0,25,45,62,78,94,108,118,125,128,115,90],"indirectPeople":[8,12,18,25,30,34,38,40,42,42,36,28],"equipmentHours":[0,400,750,1100,1450,1800,2100,2300,2450,2400,1900,1200],"nrkVolume":[0,0,0,10,25,40,55,70,82,90,60,30],"payments":[0,0,20000000,35000000,55000000,72000000,95000000,115000000,128000000,145000000,150000000,130000000],"advances":[25000000,0,0,0,0,0,0,0,0,0,0,0],"advanceOffset":[0,0,5000000,5000000,5000000,5000000,5000000,0,0,0,0,0],"factoring":[0,0,0,0,0,0,0,0,0,0,0,0],"guaranteeRate":5,"otherRevenue":[0,0,0,0,0,0,0,0,0,0,0,0]},"parameters":{"payroll":{"value":150000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"payrollTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"insurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"vacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"subcontract":{"value":0,"method":"percentRevenue","enabled":true,"lag":0,"cash":true,"vat":true},"equipment":{"value":5000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"scaffolding":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"scaffoldLabor":{"value":1500,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"projectMaterials":{"value":100,"method":"materials","enabled":true,"lag":0,"cash":true,"vat":true},"consumables":{"value":10,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"nrk":{"value":4000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"otherDirect":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"indirectPayroll":{"value":180000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"indirectTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectInsurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectVacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"food":{"value":650,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"housing":{"value":500,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"bus":{"value":639344,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"car":{"value":319672,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"formwork":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"ppe":{"value":30000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"tickets":{"value":40000,"method":"rotation","enabled":true,"lag":0,"cash":true,"vat":true},"permit":{"value":8000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"medical":{"value":3000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"vziz":{"value":20000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"office":{"value":300000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"warehouse":{"value":800000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"internet":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"waste":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"safety":{"value":1,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"accident":{"value":5000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"it":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"containers":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"modularOffice":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"transport":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"otherIndirect":{"value":10,"method":"percentDirect","enabled":true,"lag":0,"cash":true,"vat":true}},"year":2026,"vatRate":22,"vacationBasis":"annual","bindings":{},"manualCosts":{},"manualPayments":{},"dataMode":"demo"},{"id":"v2","name":"Текущая 22.09.2026","created":"2026-09-22","drivers":{"revenue":[0,25000000,48000000,64000000,82000000,108000000,132500000,150520000,164300000,178080000,159000000,121900000],"materials":[0,4000000,7000000,10000000,12000000,17000000,20000000,23000000,26000000,28000000,25000000,18000000],"directPeople":[0,25,45,62,78,94,108,118,125,128,115,90],"indirectPeople":[8,12,18,25,30,34,38,40,42,42,36,28],"equipmentHours":[0,400,750,1100,1450,1800,2100,2300,2450,2400,1900,1200],"nrkVolume":[0,0,0,10,25,40,55,70,82,90,60,30],"payments":[0,0,20000000,35000000,55000000,72000000,95000000,115000000,128000000,145000000,150000000,130000000],"advances":[25000000,0,0,0,0,0,0,0,0,0,0,0],"advanceOffset":[0,0,5000000,5000000,5000000,5000000,5000000,0,0,0,0,0],"factoring":[0,0,0,0,0,0,0,0,0,0,0,0],"guaranteeRate":5,"otherRevenue":[0,0,0,0,0,0,0,0,0,0,0,0]},"parameters":{"payroll":{"value":150000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"payrollTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"insurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"vacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"subcontract":{"value":0,"method":"percentRevenue","enabled":true,"lag":0,"cash":true,"vat":true},"equipment":{"value":5000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"scaffolding":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"scaffoldLabor":{"value":1500,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"projectMaterials":{"value":100,"method":"materials","enabled":true,"lag":0,"cash":true,"vat":true},"consumables":{"value":10,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"nrk":{"value":4000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"otherDirect":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"indirectPayroll":{"value":180000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"indirectTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectInsurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectVacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"food":{"value":650,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"housing":{"value":500,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"bus":{"value":639344,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"car":{"value":319672,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"formwork":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"ppe":{"value":30000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"tickets":{"value":40000,"method":"rotation","enabled":true,"lag":0,"cash":true,"vat":true},"permit":{"value":8000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"medical":{"value":3000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"vziz":{"value":20000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"office":{"value":300000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"warehouse":{"value":800000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"internet":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"waste":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"safety":{"value":1,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"accident":{"value":5000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"it":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"containers":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"modularOffice":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"transport":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"otherIndirect":{"value":10,"method":"percentDirect","enabled":true,"lag":0,"cash":true,"vat":true}},"year":2026,"vatRate":22,"vacationBasis":"annual","bindings":{},"manualCosts":{},"manualPayments":{},"dataMode":"demo"}],"sourceProfiles":{},"year":2026,"vacationBasis":"annual"},{"id":"d2","number":"ПС-251/24","name":"Дополнительные работы","currency":"RUB","fx":1,"vatRate":22,"parameters":{"payroll":{"value":150000,"enabled":true,"method":"monthly"},"payrollTax":{"value":13,"enabled":true,"method":"rate"},"insurance":{"value":30.9,"enabled":true,"method":"rate"},"vacation":{"value":8,"enabled":true,"method":"rate"},"subcontract":{"value":0,"enabled":true,"method":"percentRevenue"},"equipment":{"value":5000,"enabled":true,"method":"unit"},"scaffolding":{"value":0,"enabled":true,"method":"manual"},"scaffoldLabor":{"value":1500,"enabled":true,"method":"unit"},"projectMaterials":{"value":100,"enabled":true,"method":"materials"},"consumables":{"value":10,"enabled":true,"method":"percentPayroll"},"nrk":{"value":4000,"enabled":true,"method":"unit"},"otherDirect":{"value":0,"enabled":true,"method":"manual"},"indirectPayroll":{"value":180000,"enabled":true,"method":"monthly"},"indirectTax":{"value":13,"enabled":true,"method":"rate"},"indirectInsurance":{"value":30.9,"enabled":true,"method":"rate"},"indirectVacation":{"value":8,"enabled":true,"method":"rate"},"food":{"value":650,"enabled":true,"method":"day"},"housing":{"value":500,"enabled":true,"method":"day"},"bus":{"value":639344,"enabled":true,"method":"unit"},"car":{"value":319672,"enabled":true,"method":"unit"},"formwork":{"value":0,"enabled":true,"method":"manual"},"ppe":{"value":30000,"enabled":true,"method":"annualPerPerson"},"tickets":{"value":40000,"enabled":true,"method":"rotation"},"permit":{"value":8000,"enabled":true,"method":"perPerson"},"medical":{"value":3000,"enabled":true,"method":"perPerson"},"vziz":{"value":20000,"enabled":true,"method":"annualPerPerson"},"office":{"value":300000,"enabled":true,"method":"monthly"},"warehouse":{"value":800000,"enabled":true,"method":"monthly"},"internet":{"value":0,"enabled":true,"method":"monthly"},"waste":{"value":0,"enabled":true,"method":"monthly"},"safety":{"value":1,"enabled":true,"method":"percentPayroll"},"accident":{"value":5000,"enabled":true,"method":"annualPerPerson"},"it":{"value":0,"enabled":true,"method":"manual"},"containers":{"value":0,"enabled":true,"method":"manual"},"modularOffice":{"value":0,"enabled":true,"method":"manual"},"transport":{"value":0,"enabled":true,"method":"manual"},"otherIndirect":{"value":10,"enabled":true,"method":"percentDirect"}},"sources":{},"versions":[{"id":"v_mucuctuh3k83","name":"Базовая","created":"2026-09-22","drivers":{"revenue":[0,25000000,48000000,64000000,82000000,108000000,125000000,142000000,155000000,168000000,150000000,115000000],"materials":[0,4000000,7000000,10000000,12000000,17000000,20000000,23000000,26000000,28000000,25000000,18000000],"directPeople":[0,25,45,62,78,94,108,118,125,128,115,90],"indirectPeople":[8,12,18,25,30,34,38,40,42,42,36,28],"equipmentHours":[0,400,750,1100,1450,1800,2100,2300,2450,2400,1900,1200],"nrkVolume":[0,0,0,10,25,40,55,70,82,90,60,30],"payments":[0,0,20000000,35000000,55000000,72000000,95000000,115000000,128000000,145000000,150000000,130000000],"advances":[25000000,0,0,0,0,0,0,0,0,0,0,0],"advanceOffset":[0,0,5000000,5000000,5000000,5000000,5000000,0,0,0,0,0],"factoring":[0,0,0,0,0,0,0,0,0,0,0,0],"guaranteeRate":5,"otherRevenue":[0,0,0,0,0,0,0,0,0,0,0,0]},"parameters":{"payroll":{"value":150000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"payrollTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"insurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"vacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"subcontract":{"value":0,"method":"percentRevenue","enabled":true,"lag":0,"cash":true,"vat":true},"equipment":{"value":5000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"scaffolding":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"scaffoldLabor":{"value":1500,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"projectMaterials":{"value":100,"method":"materials","enabled":true,"lag":0,"cash":true,"vat":true},"consumables":{"value":10,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"nrk":{"value":4000,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"otherDirect":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"indirectPayroll":{"value":180000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":false},"indirectTax":{"value":13,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectInsurance":{"value":30.9,"method":"rate","enabled":true,"lag":0,"cash":true,"vat":false},"indirectVacation":{"value":8,"method":"rate","enabled":true,"lag":0,"cash":false,"vat":false},"food":{"value":650,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"housing":{"value":500,"method":"day","enabled":true,"lag":0,"cash":true,"vat":true},"bus":{"value":639344,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"car":{"value":319672,"method":"unit","enabled":true,"lag":0,"cash":true,"vat":true},"formwork":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"ppe":{"value":30000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"tickets":{"value":40000,"method":"rotation","enabled":true,"lag":0,"cash":true,"vat":true},"permit":{"value":8000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"medical":{"value":3000,"method":"perPerson","enabled":true,"lag":0,"cash":true,"vat":true},"vziz":{"value":20000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"office":{"value":300000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"warehouse":{"value":800000,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"internet":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"waste":{"value":0,"method":"monthly","enabled":true,"lag":0,"cash":true,"vat":true},"safety":{"value":1,"method":"percentPayroll","enabled":true,"lag":0,"cash":true,"vat":true},"accident":{"value":5000,"method":"annualPerPerson","enabled":true,"lag":0,"cash":true,"vat":true},"it":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"containers":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"modularOffice":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"transport":{"value":0,"method":"manual","enabled":true,"lag":0,"cash":true,"vat":true},"otherIndirect":{"value":10,"method":"percentDirect","enabled":true,"lag":0,"cash":true,"vat":true}},"year":2026,"vatRate":22,"vacationBasis":"annual","bindings":{},"manualCosts":{},"manualPayments":{},"dataMode":"demo"}],"sourceProfiles":{},"year":2026,"vacationBasis":"annual"}],"sourceMapping":{"schemaVersion":"1.0.0","editable":true,"matching":{"normalizeHeaders":true,"ignoreCase":true,"ignoreWhitespace":true,"ignorePunctuation":true,"minimumAutomaticConfidence":0.9,"requireConfirmationBelowConfidence":0.98},"sources":{"boq":{"enabled":true,"required":true,"path":"data/sources/boq.xlsx","sheetAliases":["BOQ","Ведомость объемов","Ведомость объёмов"],"headerRow":{"mode":"auto","fallback":9,"searchRows":30},"requiredFields":["item_code","item_name","unit","contract_quantity"],"fields":{"item_code":["Шифр ЕР","Код ЕР","Код расценки"],"item_name":["Наименование ЕР","Наименование работ"],"unit":["Ед. изм.","Единица измерения"],"contract_quantity":["Кол-во по BoQ","Количество по BOQ","Объем по BOQ","Объём по BOQ"],"labor_hours_unit":["Трудозатраты за ед., чел.-час."],"labor_hours_total":["Трудозатраты всего, чел.-час"],"machine_hours_unit":["Машины и механизмы за ед., маш.-час."],"machine_hours_total":["Машины и механизмы всего, маш.-час"],"smr_unit_rate":["Един. расценка на СМР прямые затраты, USD"],"materials_unit_rate":["Един. расценка стоимости материалов и оборудования, USD"],"kq_code":["Код KQ-1","Код KQ-2","KQ"],"kq_name":["Наименование KQ-1","Наименование KQ-2"]}},"ksg":{"enabled":true,"required":true,"path":"data/sources/ksg.xlsx","sheetAliases":["КСГ","Календарный график","График производства"],"headerRow":{"mode":"auto","fallback":2,"searchRows":20},"dynamicColumns":{"mode":"dateHeaders","grain":"month"},"requiredFields":["kq_code","work_name","planned_quantity"],"fields":{"kq_code":["Ключевые работы","Код KQ","KQ"],"work_name":["Название работы","Наименование работы"],"work_id":["Идентификатор работы","Код работы"],"smr_rate":["Расценка СМР"],"materials_rate":["Расценка МТР"],"contract_quantity":["Контрактные объемы","Контрактные объёмы"],"planned_quantity":["Кол-во по завершении","Количество по завершении"],"actual_quantity":["Фактическое количество"],"remaining_quantity":["Оставшееся количество"],"start_date":["Начало","Дата начала"],"finish_date":["Окончание","Дата окончания"]}},"personnel":{"enabled":true,"required":true,"path":"data/sources/personnel.xlsx","sheetAliases":["Персонал","График персонала","Ресурсный график персонала"],"headerRow":{"mode":"auto","fallback":4,"searchRows":20},"dynamicColumns":{"mode":"dateHeaders","grain":"day"},"requiredFields":["contractor","category","work_name","personnel_type"],"fields":{"source_key":["Ключ"],"contractor":["Подрядчик","Контрагент"],"facility":["Установка","Объект"],"title":["Титул"],"category":["Категория"],"kq_code":["KQ","Код KQ"],"discipline":["Дисциплина"],"work_name":["Наименование работ","Работа"],"personnel_type":["Персонал","Профессия","Категория персонала"]}},"equipment":{"enabled":true,"required":true,"path":"data/sources/equipment.xlsx","sheetAliases":["Техника","График техники","Ресурсный график техники"],"headerRow":{"mode":"auto","fallback":4,"searchRows":20},"dynamicColumns":{"mode":"dateHeaders","grain":"day"},"requiredFields":["contractor","equipment_type","equipment_name","work_name"],"fields":{"source_key":["Ключ"],"contractor":["Подрядчик","Контрагент"],"facility":["Установка","Объект"],"title":["Титул"],"category":["Категория"],"equipment_type":["Тип техники","Группа техники"],"equipment_name":["Техника","Наименование техники"],"work_name":["Наименование работ","Работа"],"kq_code":["KQ","Код KQ"],"discipline":["Дисциплина"]}},"primary_documents":{"enabled":true,"required":true,"path":"data/sources/primary_documents.xlsx","sheetAliases":["Первичка в вал.контракта","Первичка","КС и первичные документы"],"headerRow":{"mode":"auto","fallback":1,"searchRows":20},"requiredFields":["contractor","contract_number","currency","document_number","document_date","amount_without_vat"],"fields":{"contractor":["Контрагент","Подрядчик"],"contractor_code":["Код КА"],"legal_entity":["ЮЛ","Юридическое лицо"],"expense_type":["Вид расхода"],"contract_number":["Договор с КА","Договор","Номер договора"],"project":["Проект"],"currency":["Валюта"],"vat_rate":["Ставка НДС","НДС"],"document_number":["№ КС-3, ПУД, ТОРГ-12","Номер КС-3","Номер документа"],"document_date":["Дата КС-3","Дата подписания КС"],"amount_without_vat":["Сумма без НДС"],"services_without_vat":["Услуги без НДС"],"materials_without_vat":["МТР П без НДС"],"amount_with_vat":["Сумма с НДС"],"guarantee_rate":["% ГУ"],"guarantee_without_vat":["сумма ГУ без НДС"],"advance_offset_without_vat":["Аванс зачет без НДС","Аванс зачёт без НДС"],"planned_payment_date":["ПЛАН ОПЛАТЫ ДАТА","Плановая дата оплаты"],"actual_payment_without_vat":["Факт оплаты по КС без НДС"],"actual_payment_date":["Дата оплаты факт"]}},"payments":{"enabled":true,"required":true,"path":"data/sources/payments.xlsx","sheetAliases":["Платежи","Реестр платежей","Фактические платежи"],"headerRow":{"mode":"auto","fallback":1,"searchRows":20},"requiredFields":["payment_date","contractor","contract_number","amount_without_vat"],"fields":{"payment_date":["Дата платежа"],"contractor":["Контрагент","Имя 1","КА"],"contract_number":["Номер договора","Договор"],"currency":["Валюта транзакции"],"amount_with_vat":["Финансирование, с НДС, Влт","Финансирование, руб. экв, с НДС"],"amount_without_vat":["Финансирование, без НДС, Влт","Финансирование, руб. экв, без НДС"],"payment_purpose":["Назначение платежа"],"payment_type":["Вид оплаты (аванс, оплата по факту)"],"expense_type":["Вид расхода-формулу снизу протянуть","Вид расхода"]}},"factoring":{"enabled":true,"required":false,"path":"data/sources/factoring.xlsx","sheetAliases":["Факторинг","Реестр факторинга"],"headerRow":{"mode":"auto","fallback":1,"searchRows":20},"requiredFields":["contractor","contract_number","document_number","financed_amount"],"fields":{"contractor":["Контрагент","Подрядчик"],"project":["Проект"],"factoring_contract":["Договор на факторинге"],"contract_number":["Договор","Номер договора"],"bank":["Банк"],"financed_amount":["Оплаченная сумма банком"],"document_number":["Номер КС-3"],"document_date":["Дата КС-3"],"financing_start_date":["Дата начала начисления Процентов за пользование коммерческим кредитом3"],"financing_end_date":["Дата окончания периода коммерческого кредита6"],"amount_with_vat_currency":["Сумма в евро / Доллар с НДС"],"exchange_rate":["курс евро / доллар","Курс"],"amount_without_vat_currency":["Сумма в евро / Доллар без НДС"],"payment_date":["Дата платежа"],"amount_without_vat_rub":["Оплачено без НДС в руб."]}}}}}}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
